--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRESENCES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PRESENCES" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>81721</v>
       </c>
       <c r="C2" t="n">
-        <v>62306</v>
+        <v>19283</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3053</v>
+        <v>22254</v>
       </c>
       <c r="C3" t="n">
-        <v>63694</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>99932</v>
+        <v>40638</v>
       </c>
       <c r="C4" t="n">
-        <v>54331</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22201</v>
+        <v>66637</v>
       </c>
       <c r="C5" t="n">
-        <v>63887</v>
+        <v>62500</v>
       </c>
     </row>
     <row r="6">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92792</v>
+        <v>50002</v>
       </c>
       <c r="C6" t="n">
-        <v>63694</v>
+        <v>64413</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99998</v>
+        <v>40070</v>
       </c>
       <c r="C7" t="n">
-        <v>61856</v>
+        <v>62380</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88988</v>
+        <v>522</v>
       </c>
       <c r="C8" t="n">
-        <v>62492</v>
+        <v>62421</v>
       </c>
     </row>
     <row r="9">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29988</v>
+        <v>29837</v>
       </c>
       <c r="C9" t="n">
         <v>63694</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97306</v>
+        <v>2000</v>
       </c>
       <c r="C10" t="n">
-        <v>62358</v>
+        <v>64413</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99458</v>
+        <v>260</v>
       </c>
       <c r="C11" t="n">
         <v>62578</v>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98989</v>
+        <v>52002</v>
       </c>
       <c r="C13" t="n">
-        <v>61856</v>
+        <v>62411</v>
       </c>
     </row>
     <row r="14">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>99999</v>
+        <v>99115</v>
       </c>
       <c r="C14" t="n">
         <v>62440</v>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69943</v>
+        <v>17596</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -650,11 +650,9 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7593</v>
-      </c>
-      <c r="C18" t="n">
-        <v>62421</v>
-      </c>
+        <v>14123</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -676,10 +674,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7711</v>
+        <v>99100</v>
       </c>
       <c r="C20" t="n">
-        <v>62318</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="21">
@@ -689,11 +687,9 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44794</v>
-      </c>
-      <c r="C21" t="n">
-        <v>62578</v>
-      </c>
+        <v>89892</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -702,10 +698,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>99998</v>
+        <v>60375</v>
       </c>
       <c r="C22" t="n">
-        <v>62645</v>
+        <v>62421</v>
       </c>
     </row>
     <row r="23">
@@ -715,10 +711,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>99993</v>
+        <v>55025</v>
       </c>
       <c r="C23" t="n">
-        <v>62387</v>
+        <v>62411</v>
       </c>
     </row>
     <row r="24">
@@ -728,7 +724,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37050</v>
+        <v>36940</v>
       </c>
       <c r="C24" t="n">
         <v>63694</v>
@@ -741,7 +737,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>96822</v>
+        <v>88979</v>
       </c>
       <c r="C25" t="n">
         <v>64038</v>
@@ -767,11 +763,9 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27799</v>
-      </c>
-      <c r="C27" t="n">
-        <v>62445</v>
-      </c>
+        <v>78003</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -780,10 +774,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33139</v>
+        <v>55037</v>
       </c>
       <c r="C28" t="n">
-        <v>63694</v>
+        <v>94204</v>
       </c>
     </row>
     <row r="29">
@@ -793,7 +787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>420</v>
+        <v>93544</v>
       </c>
       <c r="C29" t="n">
         <v>63694</v>
@@ -806,10 +800,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>98988</v>
+        <v>20000</v>
       </c>
       <c r="C30" t="n">
-        <v>62579</v>
+        <v>62578</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -444,11 +444,9 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81721</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19283</v>
-      </c>
+        <v>51422</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,11 +455,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22254</v>
-      </c>
-      <c r="C3" t="n">
-        <v>63272</v>
-      </c>
+        <v>38376</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,11 +466,9 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40638</v>
-      </c>
-      <c r="C4" t="n">
-        <v>63694</v>
-      </c>
+        <v>11551</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,11 +477,9 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66637</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62500</v>
-      </c>
+        <v>31774</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,11 +488,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50002</v>
-      </c>
-      <c r="C6" t="n">
-        <v>64413</v>
-      </c>
+        <v>86666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,11 +499,9 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40070</v>
-      </c>
-      <c r="C7" t="n">
-        <v>62380</v>
-      </c>
+        <v>47511</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,11 +510,9 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>522</v>
-      </c>
-      <c r="C8" t="n">
-        <v>62421</v>
-      </c>
+        <v>11111</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,11 +521,9 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29837</v>
-      </c>
-      <c r="C9" t="n">
-        <v>63694</v>
-      </c>
+        <v>97078</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,11 +532,9 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>64413</v>
-      </c>
+        <v>31713</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,11 +543,9 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>260</v>
-      </c>
-      <c r="C11" t="n">
-        <v>62578</v>
-      </c>
+        <v>21113</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,11 +554,9 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24010</v>
-      </c>
-      <c r="C12" t="n">
-        <v>64038</v>
-      </c>
+        <v>20735</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,11 +565,9 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52002</v>
-      </c>
-      <c r="C13" t="n">
-        <v>62411</v>
-      </c>
+        <v>11761</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,11 +576,9 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>99115</v>
-      </c>
-      <c r="C14" t="n">
-        <v>62440</v>
-      </c>
+        <v>32086</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +587,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17596</v>
+        <v>36366</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -624,11 +598,9 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49915</v>
-      </c>
-      <c r="C16" t="n">
-        <v>58220</v>
-      </c>
+        <v>65578</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -637,11 +609,9 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25880</v>
-      </c>
-      <c r="C17" t="n">
-        <v>62411</v>
-      </c>
+        <v>30636</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -650,7 +620,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14123</v>
+        <v>16855</v>
       </c>
       <c r="C18" t="inlineStr"/>
     </row>
@@ -661,11 +631,9 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15016</v>
-      </c>
-      <c r="C19" t="n">
-        <v>63807</v>
-      </c>
+        <v>71678</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -674,11 +642,9 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>99100</v>
-      </c>
-      <c r="C20" t="n">
-        <v>63807</v>
-      </c>
+        <v>20110</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -687,7 +653,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>89892</v>
+        <v>83389</v>
       </c>
       <c r="C21" t="inlineStr"/>
     </row>
@@ -698,11 +664,9 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60375</v>
-      </c>
-      <c r="C22" t="n">
-        <v>62421</v>
-      </c>
+        <v>13373</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -711,11 +675,9 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55025</v>
-      </c>
-      <c r="C23" t="n">
-        <v>62411</v>
-      </c>
+        <v>77116</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -724,11 +686,9 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>36940</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63694</v>
-      </c>
+        <v>14111</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -737,11 +697,9 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>88979</v>
-      </c>
-      <c r="C25" t="n">
-        <v>64038</v>
-      </c>
+        <v>46698</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -750,11 +708,9 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>99999</v>
-      </c>
-      <c r="C26" t="n">
-        <v>61856</v>
-      </c>
+        <v>63515</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -763,7 +719,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78003</v>
+        <v>25514</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -774,11 +730,9 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>55037</v>
-      </c>
-      <c r="C28" t="n">
-        <v>94204</v>
-      </c>
+        <v>36114</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -787,11 +741,9 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>93544</v>
-      </c>
-      <c r="C29" t="n">
-        <v>63694</v>
-      </c>
+        <v>5700</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -800,11 +752,9 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C30" t="n">
-        <v>62578</v>
-      </c>
+        <v>65031</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -446,7 +446,9 @@
       <c r="B2" t="n">
         <v>51422</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>19283</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +459,9 @@
       <c r="B3" t="n">
         <v>38376</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>63272</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,7 +472,9 @@
       <c r="B4" t="n">
         <v>11551</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>63694</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -479,7 +485,9 @@
       <c r="B5" t="n">
         <v>31774</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>62500</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -490,7 +498,9 @@
       <c r="B6" t="n">
         <v>86666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>64413</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -501,7 +511,9 @@
       <c r="B7" t="n">
         <v>47511</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>62380</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -512,7 +524,9 @@
       <c r="B8" t="n">
         <v>11111</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>62421</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,7 +537,9 @@
       <c r="B9" t="n">
         <v>97078</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>63694</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -534,7 +550,9 @@
       <c r="B10" t="n">
         <v>31713</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>64413</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -545,7 +563,9 @@
       <c r="B11" t="n">
         <v>21113</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>62578</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -556,7 +576,9 @@
       <c r="B12" t="n">
         <v>20735</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>64038</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -567,7 +589,9 @@
       <c r="B13" t="n">
         <v>11761</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>62411</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -578,7 +602,9 @@
       <c r="B14" t="n">
         <v>32086</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>62440</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -600,7 +626,9 @@
       <c r="B16" t="n">
         <v>65578</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>58220</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -611,7 +639,9 @@
       <c r="B17" t="n">
         <v>30636</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>62411</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -633,7 +663,9 @@
       <c r="B19" t="n">
         <v>71678</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>63807</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -644,7 +676,9 @@
       <c r="B20" t="n">
         <v>20110</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>63807</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -666,7 +700,9 @@
       <c r="B22" t="n">
         <v>13373</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>62421</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -677,7 +713,9 @@
       <c r="B23" t="n">
         <v>77116</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>62411</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -688,7 +726,9 @@
       <c r="B24" t="n">
         <v>14111</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>63694</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -699,7 +739,9 @@
       <c r="B25" t="n">
         <v>46698</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>64038</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -710,7 +752,9 @@
       <c r="B26" t="n">
         <v>63515</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>61856</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -732,7 +776,9 @@
       <c r="B28" t="n">
         <v>36114</v>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>94204</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -743,7 +789,9 @@
       <c r="B29" t="n">
         <v>5700</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>63694</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -754,7 +802,9 @@
       <c r="B30" t="n">
         <v>65031</v>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>62578</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51422</v>
+        <v>19283</v>
       </c>
       <c r="C2" t="n">
-        <v>19283</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38376</v>
+        <v>50305</v>
       </c>
       <c r="C3" t="n">
-        <v>63272</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11551</v>
+        <v>54331</v>
       </c>
       <c r="C4" t="n">
-        <v>63694</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="5">
@@ -483,11 +483,9 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31774</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62500</v>
-      </c>
+        <v>58220</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,10 +494,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86666</v>
+        <v>58927</v>
       </c>
       <c r="C6" t="n">
-        <v>64413</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="7">
@@ -509,301 +507,348 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47511</v>
+        <v>61856</v>
       </c>
       <c r="C7" t="n">
-        <v>62380</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62034.jpeg</t>
+          <t>EXAM_FORM1_61992.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11111</v>
+        <v>61992</v>
       </c>
       <c r="C8" t="n">
-        <v>62421</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62298.jpeg</t>
+          <t>EXAM_FORM1_62034.jpeg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97078</v>
+        <v>62034</v>
       </c>
       <c r="C9" t="n">
-        <v>63694</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62358.jpeg</t>
+          <t>EXAM_FORM1_62288.png</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31713</v>
+        <v>62288</v>
       </c>
       <c r="C10" t="n">
-        <v>64413</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62380.jpeg</t>
+          <t>EXAM_FORM1_62298.jpeg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21113</v>
+        <v>62298</v>
       </c>
       <c r="C11" t="n">
-        <v>62578</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62401.jpg</t>
+          <t>EXAM_FORM1_62336.JPG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20735</v>
+        <v>62336</v>
       </c>
       <c r="C12" t="n">
-        <v>64038</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62436.jpeg</t>
+          <t>EXAM_FORM1_62358.jpeg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11761</v>
+        <v>62358</v>
       </c>
       <c r="C13" t="n">
-        <v>62411</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62440.jpeg</t>
+          <t>EXAM_FORM1_62380.jpeg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32086</v>
+        <v>62380</v>
       </c>
       <c r="C14" t="n">
-        <v>62440</v>
+        <v>62578</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62445.jpg</t>
+          <t>EXAM_FORM1_62401.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36366</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>62401</v>
+      </c>
+      <c r="C15" t="n">
+        <v>62578</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62578.jpg</t>
+          <t>EXAM_FORM1_62436.jpeg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>65578</v>
+        <v>62436</v>
       </c>
       <c r="C16" t="n">
-        <v>58220</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62598.jpg</t>
+          <t>EXAM_FORM1_62440.jpeg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30636</v>
+        <v>62440</v>
       </c>
       <c r="C17" t="n">
-        <v>62411</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62616.jpg</t>
+          <t>EXAM_FORM1_62445.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16855</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>62485</v>
+      </c>
+      <c r="C18" t="n">
+        <v>19283</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62645.jpeg</t>
+          <t>EXAM_FORM1_62578.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71678</v>
+        <v>62578</v>
       </c>
       <c r="C19" t="n">
-        <v>63807</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62766.jpg</t>
+          <t>EXAM_FORM1_62598.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20110</v>
+        <v>62598</v>
       </c>
       <c r="C20" t="n">
-        <v>63807</v>
+        <v>62306</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63029.jpg</t>
+          <t>EXAM_FORM1_62616.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83389</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>62616</v>
+      </c>
+      <c r="C21" t="n">
+        <v>62336</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63272.jpg</t>
+          <t>EXAM_FORM1_62645.jpeg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13373</v>
+        <v>62645</v>
       </c>
       <c r="C22" t="n">
-        <v>62421</v>
+        <v>62645</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63273.jpg</t>
+          <t>EXAM_FORM1_62766.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>77116</v>
+        <v>9001</v>
       </c>
       <c r="C23" t="n">
-        <v>62411</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63694.jpg</t>
+          <t>EXAM_FORM1_63029.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14111</v>
+        <v>63629</v>
       </c>
       <c r="C24" t="n">
-        <v>63694</v>
+        <v>62336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63807.jpeg</t>
+          <t>EXAM_FORM1_63272.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>46698</v>
+        <v>63202</v>
       </c>
       <c r="C25" t="n">
-        <v>64038</v>
+        <v>62306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63836.jpg</t>
+          <t>EXAM_FORM1_63273.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63515</v>
+        <v>63273</v>
       </c>
       <c r="C26" t="n">
-        <v>61856</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63887.jpeg</t>
+          <t>EXAM_FORM1_63694.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25514</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>63694</v>
+      </c>
+      <c r="C27" t="n">
+        <v>62421</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_64413.jpg</t>
+          <t>EXAM_FORM1_63807.jpeg</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36114</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>94204</v>
+        <v>19283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_65442.jpg</t>
+          <t>EXAM_FORM1_63836.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5700</v>
+        <v>63836</v>
       </c>
       <c r="C29" t="n">
-        <v>63694</v>
+        <v>62572</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>EXAM_FORM1_63887.jpeg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>63887</v>
+      </c>
+      <c r="C30" t="n">
+        <v>63694</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXAM_FORM1_64413.jpg</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>64413</v>
+      </c>
+      <c r="C31" t="n">
+        <v>63694</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EXAM_FORM1_65442.jpg</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>65442</v>
+      </c>
+      <c r="C32" t="n">
+        <v>62298</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>EXAM_FORM1_75012.jpg</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>65031</v>
-      </c>
-      <c r="C30" t="n">
-        <v>62578</v>
+      <c r="B33" t="n">
+        <v>75012</v>
+      </c>
+      <c r="C33" t="n">
+        <v>62298</v>
       </c>
     </row>
   </sheetData>
